--- a/[Document]/소개운영자료/DIVE_개인정보_진로현황_수요조사.xlsx
+++ b/[Document]/소개운영자료/DIVE_개인정보_진로현황_수요조사.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DataScience\[DIVE]\[Document]\소개운영자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F266EA-B8D1-4E03-8D79-578637ECF02E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846E2D9B-D3AD-4F9C-8D54-D51DA18F7808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31890" yWindow="-110" windowWidth="38620" windowHeight="21820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="51110" yWindow="0" windowWidth="19380" windowHeight="21690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026Y1Q" sheetId="1" r:id="rId1"/>
@@ -6811,73 +6811,507 @@
     <phoneticPr fontId="26" type="noConversion"/>
   </si>
   <si>
-    <t>추가 도메인 기반 논문 작성 + 코드 그대로</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>고려대학교 경영학과&gt;토스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인턴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> &gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인천대학교</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>무역학부</t>
+    </r>
     <phoneticPr fontId="26" type="noConversion"/>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>고려대학교 경영학과&gt;토스</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>인턴</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> &gt; </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>인천대학교</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>무역학부</t>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정도로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>후보</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">리스트업
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>논문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">필요
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>로그데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> SQL
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한국</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>HCI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>학회</t>
+    </r>
+    <phoneticPr fontId="26" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문제</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>압축(한국 R&amp;D 예산배분 논문)
+분석기획/결과설득력</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>논문작성법동영상공유??</t>
+    </r>
+    <phoneticPr fontId="26" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>추가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>도메인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>논문</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>코드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그대로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
+(1) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>채널 터치 벡터화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+(2) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>물리학 속도&amp;가독도 반영 (반응속도론)</t>
     </r>
     <phoneticPr fontId="26" type="noConversion"/>
   </si>
@@ -6917,277 +7351,6 @@
         <charset val="129"/>
       </rPr>
       <t>무섭다?? 인간이 할일;;</t>
-    </r>
-    <phoneticPr fontId="26" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>개</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>정도로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>후보</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">리스트업
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>논문</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>작성</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">필요
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>로그데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> SQL
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>한국</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>HCI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>학회</t>
-    </r>
-    <phoneticPr fontId="26" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>개로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>문제</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>압축(한국 R&amp;D 예산배분 논문)
-분석기획/결과설득력</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>+</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>논문작성법동영상공유??</t>
     </r>
     <phoneticPr fontId="26" type="noConversion"/>
   </si>
@@ -7196,7 +7359,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7402,6 +7565,13 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -7509,7 +7679,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -7623,6 +7793,9 @@
     <xf numFmtId="0" fontId="30" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -7635,7 +7808,7 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7871,11 +8044,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="60.75" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="41"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="42"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -7888,34 +8061,34 @@
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
       <c r="I2" s="5"/>
       <c r="J2" s="6"/>
-      <c r="K2" s="44" t="s">
+      <c r="K2" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="44" t="s">
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="44" t="s">
+      <c r="P2" s="41"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="S2" s="40"/>
-      <c r="T2" s="40"/>
-      <c r="U2" s="41"/>
+      <c r="S2" s="41"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="42"/>
       <c r="V2" s="7" t="s">
         <v>6</v>
       </c>
@@ -8168,7 +8341,7 @@
         <v>65</v>
       </c>
       <c r="I7" s="38" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J7" s="16"/>
       <c r="K7" s="24"/>
@@ -8327,8 +8500,8 @@
       <c r="V10" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="W10" s="45" t="s">
-        <v>196</v>
+      <c r="W10" s="39" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="118.15">
@@ -8525,7 +8698,7 @@
         <v>125</v>
       </c>
       <c r="W14" s="37" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="28.5">
@@ -8619,8 +8792,8 @@
       <c r="V16" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="W16" s="29" t="s">
-        <v>194</v>
+      <c r="W16" s="46" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:23" ht="28.5">
@@ -8762,8 +8935,8 @@
       <c r="V19" s="29" t="s">
         <v>161</v>
       </c>
-      <c r="W19" s="45" t="s">
-        <v>198</v>
+      <c r="W19" s="39" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:23" ht="33.75">
